--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260708.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.77%</t>
+          <t>10.78%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.86%</t>
+          <t>8.94%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.38%</t>
+          <t>8.18%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.63%</t>
+          <t>7.50%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,334,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.77%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,382,000</t>
+          <t>6,334,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.59%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.16%</t>
         </is>
       </c>
     </row>
@@ -770,112 +770,112 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.80%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>5,191,000</t>
+          <t>2,417,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.46%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,417,000</t>
+          <t>5,191,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.41%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>4,833,848</t>
+          <t>8,949,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,052,000</t>
+          <t>8,315,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.50%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>8,315,000</t>
+          <t>5,052,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,66 +887,66 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>8,949,000</t>
+          <t>4,833,848</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.36%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12,742,000</t>
+          <t>5,160,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,160,000</t>
+          <t>12,742,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,811,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>1,811,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1107,39 +1107,39 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>411,000</t>
+          <t>3,528,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>3,528,000</t>
+          <t>411,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,628,939,793</t>
+          <t>4,369,542,800</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-294,893,156</t>
+          <t>-692,265,646</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
